--- a/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
+++ b/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
@@ -195,12 +195,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Инструментальные средства разработки»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, какие инструменты сопровождают разработку от редактора до развёртывания и как выбрать минимальный набор под учебный проект.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Инструментальные средства разработки</t>
+          <t xml:space="preserve">редактор, IDE, система сборки, контроль версий, отладчик, CI</t>
         </is>
       </c>
     </row>
@@ -225,16 +225,16 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «VS Code: возможности и настройка»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете устройство VS Code: редактор, панель проводника, палитра команд, настройки и рабочее пространство проекта.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VS Code: возможности и настройка</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t xml:space="preserve">палитра команд, settings.json, рабочее пространство, проводник, терминал</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">3-4</t>
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Настройка VS Code; Настройка Visual Studio 2026.</t>
+          <t xml:space="preserve">Настраиваете обе среды под Python и C#: тема, шрифт, расширения, интерпретатор, набор инструментов C++ и сдаёте скриншоты настроек с коротким пояснением.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Настройка VS Code, Настройка Visual Studio 2026</t>
+          <t xml:space="preserve">настройки VS Code, рабочая нагрузка, интерпретатор, расширение, сборка проекта</t>
         </is>
       </c>
     </row>
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Visual Studio 2026 Community»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете устройство Visual Studio: решение и проект, обозреватель решений, конструктор форм и окна отладки для C#.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual Studio 2026 Community</t>
+          <t xml:space="preserve">решение, проект, обозреватель решений, шаблон проекта, конструктор форм</t>
         </is>
       </c>
     </row>
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Расширения и плагины»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, как расширения добавляют языки, линтеры и отладчики, и как проверить расширение перед установкой в учебную среду.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Расширения и плагины</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t xml:space="preserve">расширение, маркетплейс, пакет расширений, языковая поддержка, производительность</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">7-8</t>
@@ -345,12 +345,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Git и GitHub; Виртуальное окружение Python.</t>
+          <t xml:space="preserve">Заводите репозиторий проекта на GitHub, делаете ветку и коммиты, создаёте виртуальное окружение и сдаёте ссылку на репозиторий с файлом зависимостей.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Git и GitHub, Виртуальное окружение Python</t>
+          <t xml:space="preserve">git init, коммит, ветка, GitHub, venv, requirements.txt</t>
         </is>
       </c>
     </row>
@@ -375,12 +375,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Git и GitHub»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете три зоны Git: рабочую папку, индекс и репозиторий, а также что делает коммит и чем ветка отличается от копии папки.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Git и GitHub</t>
+          <t xml:space="preserve">рабочая папка, индекс, коммит, ветка, удалённый репозиторий, слияние</t>
         </is>
       </c>
     </row>
@@ -405,12 +405,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Сборка проекта»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Собираете проект из исходников в исполняемый файл, разбираете сообщения сборки и сдаёте артефакт с журналом ошибок и их исправлений.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сборка проекта</t>
+          <t xml:space="preserve">сборка, артефакт, ошибка компиляции, командная строка, журнал сборки</t>
         </is>
       </c>
     </row>
@@ -435,12 +435,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Системы сборки»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, что делает система сборки: находит зависимости, вызывает компилятор, линкует модули и пересобирает только изменённое.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Системы сборки</t>
+          <t xml:space="preserve">компиляция, линковка, зависимость, инкрементальная сборка, артефакт</t>
         </is>
       </c>
     </row>
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Виртуальные окружения Python»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, зачем проекту своё окружение, как оно изолирует пакеты и что происходит с глобальным Python при установке зависимостей.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виртуальные окружения Python</t>
+          <t xml:space="preserve">venv, интерпретатор, site-packages, requirements.txt, изоляция зависимостей</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Отладка в VS Code; Отладка в Visual Studio.</t>
+          <t xml:space="preserve">Ищете ошибку в двух проектах: ставите точки останова, смотрите стек вызовов и переменные, исправляете код и сдаёте отчёт с причиной сбоя.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отладка в VS Code, Отладка в Visual Studio</t>
+          <t xml:space="preserve">точка останова, стек вызовов, шаг с обходом, переменные, конфигурация запуска</t>
         </is>
       </c>
     </row>
@@ -525,16 +525,16 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Пакетные менеджеры»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, как pip и NuGet находят пакет, проверяют версии зависимостей и почему без фиксации версий сборка ломается на другой машине.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пакетные менеджеры</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t xml:space="preserve">pip, NuGet, пакет, версия, зависимость, lock-файл</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -555,16 +555,16 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Отладчик»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете устройство отладчика: точка останова, пошаговое выполнение, стек вызовов, точки наблюдения и как читать состояние программы.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отладчик</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+          <t xml:space="preserve">отладчик, точка останова, стек вызовов, точка наблюдения, пошаговое выполнение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17-18</t>
@@ -585,12 +585,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Линтер и форматтер; Статический анализ.</t>
+          <t xml:space="preserve">Прогоняете учебный проект через линтер, форматтер и анализатор типов, исправляете замечания и сдаёте отчёт до и после с числом предупреждений.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Линтер и форматтер, Статический анализ</t>
+          <t xml:space="preserve">предупреждение, правило, конфигурация, автоформат, отчёт, типизация</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Профилирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, как найти узкое место программы: время выполнения, число вызовов функций и профиль по строкам вместо догадок.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профилирование</t>
+          <t xml:space="preserve">профилировщик, узкое место, время выполнения, вызов функции, отчёт</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Тестирование в IDE»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Пишете модульные тесты для функции учебного проекта, запускаете их из IDE и сдаёте набор тестов с отчётом о прохождении и падении.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование в IDE</t>
+          <t xml:space="preserve">модульный тест, assert, тестовый набор, отчёт, падение теста</t>
         </is>
       </c>
     </row>
@@ -675,12 +675,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Линтеры и форматтеры»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете разницу между линтером и форматтером: один ищет проблемы в коде, другой приводит запись к единому виду.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Линтеры и форматтеры</t>
+          <t xml:space="preserve">правило, стиль кода, конфигурация, предупреждение, автоформат</t>
         </is>
       </c>
     </row>
@@ -705,16 +705,16 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Статический анализ»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, что статический анализ находит без запуска программы: неиспользуемые переменные, ошибки типов и потенциальные падения.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статический анализ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+          <t xml:space="preserve">статический анализ, анализ типов, дефект, ложное срабатывание, динамический анализ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">23-24</t>
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Postman; SQLiteOnline.</t>
+          <t xml:space="preserve">Проверяете учебный API в Postman: собираете коллекцию с тестами кода ответа и тела JSON, параллельно готовите базу в SQLiteOnline и сдаёте коллекцию и SQL-скрипт.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postman, SQLiteOnline</t>
+          <t xml:space="preserve">коллекция, тест ответа, JSON, SQL-скрипт, переменная окружения</t>
         </is>
       </c>
     </row>
@@ -765,16 +765,16 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Тестирование в IDE»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, как тесты живут внутри проекта: где лежат файлы тестов, как IDE их находит и что показывает отчёт о покрытии.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование в IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+          <t xml:space="preserve">тестовый файл, обнаружение тестов, отчёт, покрытие, фикстура</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">26</t>
@@ -795,16 +795,16 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Postman»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете устройство Postman: коллекция, окружение, переменные и тесты, которые проверяют ответ автоматически.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postman</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+          <t xml:space="preserve">коллекция, окружение, переменная, запрос, тест ответа</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">27-28</t>
@@ -825,12 +825,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: VirtualBox; GitHub Actions.</t>
+          <t xml:space="preserve">Поднимаете учебную Linux в VirtualBox с пробросом порта по SSH и настраиваете workflow GitHub Actions, который собирает проект при каждом push.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VirtualBox, GitHub Actions</t>
+          <t xml:space="preserve">NAT, проброс порта, SSH, workflow, виртуальная машина, гостевая ОС</t>
         </is>
       </c>
     </row>
@@ -855,16 +855,16 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «SQLite и sqliteonline.com»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, как устроена база SQLite: один файл, таблицы, схема и почему сервис sqliteonline.com удобен для учебных запросов без установки.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SQLite и sqliteonline.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t xml:space="preserve">файл базы, схема, SQL-запрос, перенос базы, встроенная СУБД</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
@@ -885,12 +885,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Документирование»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Оформляете документацию к учебному проекту: README с установкой и запуском, описание структуры, и сдаёте документ, по которому проект запускает другой студент.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документирование</t>
+          <t xml:space="preserve">README, инструкция запуска, структура проекта, Markdown, документация</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Виртуальные машины в разработке»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, зачем разработчику виртуальная машина: изоляция окружения, проверка на другой ОС и воспроизводимость стенда.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виртуальные машины в разработке</t>
+          <t xml:space="preserve">гипервизор, виртуальная машина, NAT, мост, снимок состояния</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Профилирование»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Профилируете медленную функцию учебного проекта, находите узкое место по отчёту и сдаёте исправленный вариант с замером времени до и после.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профилирование</t>
+          <t xml:space="preserve">профилировщик, узкое место, замер времени, оптимизация, отчёт</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «CI/CD и GitHub Actions»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете конвейер CI/CD: что запускается на каждый коммит, из каких шагов состоит workflow и где хранятся секреты.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CI/CD и GitHub Actions</t>
+          <t xml:space="preserve">непрерывная интеграция, непрерывная доставка, workflow, job, шаг, секрет</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Мини-проект»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Собираете небольшой проект целиком: репозиторий, окружение, сборка, тесты и README, и сдаёте ссылку с проходящим workflow проверок.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мини-проект</t>
+          <t xml:space="preserve">мини-проект, репозиторий, workflow, тесты, README</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Документирование кода»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, как документировать код изнутри: docstring, комментарии к сложным местам и автогенерация справки из аннотаций.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документирование кода</t>
+          <t xml:space="preserve">docstring, комментарий, аннотация типа, автодокументация, стиль</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Автоматизация проверок»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Собираете локальный скрипт проверок: линтер, тесты и сборка одной командой, и сдаёте конфигурацию, которая возвращает понятный код ошибки.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Автоматизация проверок</t>
+          <t xml:space="preserve">скрипт проверок, линтер, тесты, сборка, код возврата</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Выбор инструментов под задачу»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете критерии выбора инструмента: размер проекта, язык, требования к сборке и стоимость поддержки, и сравниваете пары альтернатив.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выбор инструментов под задачу</t>
+          <t xml:space="preserve">критерии выбора, альтернатива, стоимость поддержки, масштаб проекта, экосистема</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговый проект»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Сдаёте итоговый проект с полным набором инструментов: репозиторий, окружение, сборка, отладка, тесты, документация и работающий workflow.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговый проект</t>
+          <t xml:space="preserve">итоговый проект, репозиторий, сборка, тесты, документация, защита</t>
         </is>
       </c>
     </row>

--- a/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
+++ b/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>3420</v>
+        <v>76</v>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>

--- a/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
+++ b/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
@@ -247,7 +247,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Настройка VS Code; Настройка Visual Studio 2026</t>
+          <t xml:space="preserve">Практика 1. Настройка VS Code; Настройка Visual Studio 2022</t>
         </is>
       </c>
       <c r="D8" s="6">
@@ -277,7 +277,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. Visual Studio 2026 Community</t>
+          <t xml:space="preserve">Лекция 3. Visual Studio 2022 Community</t>
         </is>
       </c>
       <c r="D9" s="6">

--- a/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
+++ b/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
@@ -234,63 +234,63 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция 3. Visual Studio 2022 Community</t>
+        </is>
+      </c>
+      <c r="D8" s="6">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разбираете устройство Visual Studio: решение и проект, обозреватель решений, конструктор форм и окна отладки для C#.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">решение, проект, обозреватель решений, шаблон проекта, конструктор форм</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 1. Настройка VS Code; Настройка Visual Studio 2022</t>
         </is>
       </c>
-      <c r="D8" s="6">
+      <c r="D9" s="6">
         <v>4</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Настраиваете обе среды под Python и C#: тема, шрифт, расширения, интерпретатор, набор инструментов C++ и сдаёте скриншоты настроек с коротким пояснением.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">настройки VS Code, рабочая нагрузка, интерпретатор, расширение, сборка проекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 3. Visual Studio 2022 Community</t>
-        </is>
-      </c>
-      <c r="D9" s="6">
-        <v>2</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разбираете устройство Visual Studio: решение и проект, обозреватель решений, конструктор форм и окна отладки для C#.</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">решение, проект, обозреватель решений, шаблон проекта, конструктор форм</t>
         </is>
       </c>
     </row>
@@ -324,40 +324,40 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Git и GitHub; Виртуальное окружение Python</t>
+          <t xml:space="preserve">Лекция 5. Git и GitHub</t>
         </is>
       </c>
       <c r="D11" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заводите репозиторий проекта на GitHub, делаете ветку и коммиты, создаёте виртуальное окружение и сдаёте ссылку на репозиторий с файлом зависимостей.</t>
+          <t xml:space="preserve">Разбираете три зоны Git: рабочую папку, индекс и репозиторий, а также что делает коммит и чем ветка отличается от копии папки.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">git init, коммит, ветка, GitHub, venv, requirements.txt</t>
+          <t xml:space="preserve">рабочая папка, индекс, коммит, ветка, удалённый репозиторий, слияние</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -367,7 +367,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. Git и GitHub</t>
+          <t xml:space="preserve">Лекция 6. Системы сборки</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -375,19 +375,19 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете три зоны Git: рабочую папку, индекс и репозиторий, а также что делает коммит и чем ветка отличается от копии папки.</t>
+          <t xml:space="preserve">Разбираете, что делает система сборки: находит зависимости, вызывает компилятор, линкует модули и пересобирает только изменённое.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">рабочая папка, индекс, коммит, ветка, удалённый репозиторий, слияние</t>
+          <t xml:space="preserve">компиляция, линковка, зависимость, инкрементальная сборка, артефакт</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -397,7 +397,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Сборка проекта</t>
+          <t xml:space="preserve">Практика 2. Сборка проекта</t>
         </is>
       </c>
       <c r="D13" s="6">
@@ -417,7 +417,7 @@
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. Системы сборки</t>
+          <t xml:space="preserve">Лекция 7. Виртуальные окружения Python</t>
         </is>
       </c>
       <c r="D14" s="6">
@@ -435,79 +435,79 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, что делает система сборки: находит зависимости, вызывает компилятор, линкует модули и пересобирает только изменённое.</t>
+          <t xml:space="preserve">Разбираете, зачем проекту своё окружение, как оно изолирует пакеты и что происходит с глобальным Python при установке зависимостей.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">компиляция, линковка, зависимость, инкрементальная сборка, артефакт</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t xml:space="preserve">venv, интерпретатор, site-packages, requirements.txt, изоляция зависимостей</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11-12</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 7. Виртуальные окружения Python</t>
+          <t xml:space="preserve">Практика 3. Git и GitHub; Виртуальное окружение Python</t>
         </is>
       </c>
       <c r="D15" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, зачем проекту своё окружение, как оно изолирует пакеты и что происходит с глобальным Python при установке зависимостей.</t>
+          <t xml:space="preserve">Заводите репозиторий проекта на GitHub, делаете ветку и коммиты, создаёте виртуальное окружение и сдаёте ссылку на репозиторий с файлом зависимостей.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">venv, интерпретатор, site-packages, requirements.txt, изоляция зависимостей</t>
+          <t xml:space="preserve">git init, коммит, ветка, GitHub, venv, requirements.txt</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13-14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Отладка в VS Code; Отладка в Visual Studio</t>
+          <t xml:space="preserve">Лекция 8. Пакетные менеджеры</t>
         </is>
       </c>
       <c r="D16" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ищете ошибку в двух проектах: ставите точки останова, смотрите стек вызовов и переменные, исправляете код и сдаёте отчёт с причиной сбоя.</t>
+          <t xml:space="preserve">Разбираете, как pip и NuGet находят пакет, проверяют версии зависимостей и почему без фиксации версий сборка ломается на другой машине.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">точка останова, стек вызовов, шаг с обходом, переменные, конфигурация запуска</t>
+          <t xml:space="preserve">pip, NuGet, пакет, версия, зависимость, lock-файл</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Пакетные менеджеры</t>
+          <t xml:space="preserve">Лекция 9. Отладчик</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -525,89 +525,89 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, как pip и NuGet находят пакет, проверяют версии зависимостей и почему без фиксации версий сборка ломается на другой машине.</t>
+          <t xml:space="preserve">Разбираете устройство отладчика: точка останова, пошаговое выполнение, стек вызовов, точки наблюдения и как читать состояние программы.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pip, NuGet, пакет, версия, зависимость, lock-файл</t>
+          <t xml:space="preserve">отладчик, точка останова, стек вызовов, точка наблюдения, пошаговое выполнение</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15-16</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Отладчик</t>
+          <t xml:space="preserve">Практика 4. Отладка в VS Code; Отладка в Visual Studio</t>
         </is>
       </c>
       <c r="D18" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете устройство отладчика: точка останова, пошаговое выполнение, стек вызовов, точки наблюдения и как читать состояние программы.</t>
+          <t xml:space="preserve">Ищете ошибку в двух проектах: ставите точки останова, смотрите стек вызовов и переменные, исправляете код и сдаёте отчёт с причиной сбоя.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">отладчик, точка останова, стек вызовов, точка наблюдения, пошаговое выполнение</t>
+          <t xml:space="preserve">точка останова, стек вызовов, шаг с обходом, переменные, конфигурация запуска</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-18</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Линтер и форматтер; Статический анализ</t>
+          <t xml:space="preserve">Лекция 10. Профилирование</t>
         </is>
       </c>
       <c r="D19" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Прогоняете учебный проект через линтер, форматтер и анализатор типов, исправляете замечания и сдаёте отчёт до и после с числом предупреждений.</t>
+          <t xml:space="preserve">Разбираете, как найти узкое место программы: время выполнения, число вызовов функций и профиль по строкам вместо догадок.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">предупреждение, правило, конфигурация, автоформат, отчёт, типизация</t>
+          <t xml:space="preserve">профилировщик, узкое место, время выполнения, вызов функции, отчёт</t>
         </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Профилирование</t>
+          <t xml:space="preserve">Практика 5. Профилирование</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,29 +615,29 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, как найти узкое место программы: время выполнения, число вызовов функций и профиль по строкам вместо догадок.</t>
+          <t xml:space="preserve">Профилируете медленную функцию учебного проекта, находите узкое место по отчёту и сдаёте исправленный вариант с замером времени до и после.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">профилировщик, узкое место, время выполнения, вызов функции, отчёт</t>
+          <t xml:space="preserve">профилировщик, узкое место, замер времени, оптимизация, отчёт</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Тестирование в IDE</t>
+          <t xml:space="preserve">Лекция 11. Линтеры и форматтеры</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -645,19 +645,19 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пишете модульные тесты для функции учебного проекта, запускаете их из IDE и сдаёте набор тестов с отчётом о прохождении и падении.</t>
+          <t xml:space="preserve">Разбираете разницу между линтером и форматтером: один ищет проблемы в коде, другой приводит запись к единому виду.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">модульный тест, assert, тестовый набор, отчёт, падение теста</t>
+          <t xml:space="preserve">правило, стиль кода, конфигурация, предупреждение, автоформат</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Линтеры и форматтеры</t>
+          <t xml:space="preserve">Лекция 12. Статический анализ</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,89 +675,89 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете разницу между линтером и форматтером: один ищет проблемы в коде, другой приводит запись к единому виду.</t>
+          <t xml:space="preserve">Разбираете, что статический анализ находит без запуска программы: неиспользуемые переменные, ошибки типов и потенциальные падения.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">правило, стиль кода, конфигурация, предупреждение, автоформат</t>
+          <t xml:space="preserve">статический анализ, анализ типов, дефект, ложное срабатывание, динамический анализ</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21-22</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Статический анализ</t>
+          <t xml:space="preserve">Практика 6. Линтер и форматтер; Статический анализ</t>
         </is>
       </c>
       <c r="D23" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, что статический анализ находит без запуска программы: неиспользуемые переменные, ошибки типов и потенциальные падения.</t>
+          <t xml:space="preserve">Прогоняете учебный проект через линтер, форматтер и анализатор типов, исправляете замечания и сдаёте отчёт до и после с числом предупреждений.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">статический анализ, анализ типов, дефект, ложное срабатывание, динамический анализ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
+          <t xml:space="preserve">предупреждение, правило, конфигурация, автоформат, отчёт, типизация</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Postman; SQLiteOnline</t>
+          <t xml:space="preserve">Лекция 13. Тестирование в IDE</t>
         </is>
       </c>
       <c r="D24" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверяете учебный API в Postman: собираете коллекцию с тестами кода ответа и тела JSON, параллельно готовите базу в SQLiteOnline и сдаёте коллекцию и SQL-скрипт.</t>
+          <t xml:space="preserve">Разбираете, как тесты живут внутри проекта: где лежат файлы тестов, как IDE их находит и что показывает отчёт о покрытии.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">коллекция, тест ответа, JSON, SQL-скрипт, переменная окружения</t>
+          <t xml:space="preserve">тестовый файл, обнаружение тестов, отчёт, покрытие, фикстура</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 13. Тестирование в IDE</t>
+          <t xml:space="preserve">Практика 7. Тестирование в IDE</t>
         </is>
       </c>
       <c r="D25" s="6">
@@ -765,19 +765,19 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, как тесты живут внутри проекта: где лежат файлы тестов, как IDE их находит и что показывает отчёт о покрытии.</t>
+          <t xml:space="preserve">Пишете модульные тесты для функции учебного проекта, запускаете их из IDE и сдаёте набор тестов с отчётом о прохождении и падении.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">тестовый файл, обнаружение тестов, отчёт, покрытие, фикстура</t>
+          <t xml:space="preserve">модульный тест, assert, тестовый набор, отчёт, падение теста</t>
         </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -807,77 +807,77 @@
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 15. SQLite и sqliteonline.com</t>
+        </is>
+      </c>
+      <c r="D27" s="6">
+        <v>2</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разбираете, как устроена база SQLite: один файл, таблицы, схема и почему сервис sqliteonline.com удобен для учебных запросов без установки.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">файл базы, схема, SQL-запрос, перенос базы, встроенная СУБД</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">27-28</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 8. VirtualBox; GitHub Actions</t>
-        </is>
-      </c>
-      <c r="D27" s="6">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика 8. Postman; SQLiteOnline</t>
+        </is>
+      </c>
+      <c r="D28" s="6">
         <v>4</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Поднимаете учебную Linux в VirtualBox с пробросом порта по SSH и настраиваете workflow GitHub Actions, который собирает проект при каждом push.</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NAT, проброс порта, SSH, workflow, виртуальная машина, гостевая ОС</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проверяете учебный API в Postman: собираете коллекцию с тестами кода ответа и тела JSON, параллельно готовите базу в SQLiteOnline и сдаёте коллекцию и SQL-скрипт.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">коллекция, тест ответа, JSON, SQL-скрипт, переменная окружения</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 15. SQLite и sqliteonline.com</t>
-        </is>
-      </c>
-      <c r="D28" s="6">
-        <v>2</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разбираете, как устроена база SQLite: один файл, таблицы, схема и почему сервис sqliteonline.com удобен для учебных запросов без установки.</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">файл базы, схема, SQL-запрос, перенос базы, встроенная СУБД</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Документирование</t>
+          <t xml:space="preserve">Лекция 16. Виртуальные машины в разработке</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -885,19 +885,19 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оформляете документацию к учебному проекту: README с установкой и запуском, описание структуры, и сдаёте документ, по которому проект запускает другой студент.</t>
+          <t xml:space="preserve">Разбираете, зачем разработчику виртуальная машина: изоляция окружения, проверка на другой ОС и воспроизводимость стенда.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">README, инструкция запуска, структура проекта, Markdown, документация</t>
+          <t xml:space="preserve">гипервизор, виртуальная машина, NAT, мост, снимок состояния</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. Виртуальные машины в разработке</t>
+          <t xml:space="preserve">Лекция 17. CI/CD и GitHub Actions</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,19 +915,19 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, зачем разработчику виртуальная машина: изоляция окружения, проверка на другой ОС и воспроизводимость стенда.</t>
+          <t xml:space="preserve">Разбираете конвейер CI/CD: что запускается на каждый коммит, из каких шагов состоит workflow и где хранятся секреты.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">гипервизор, виртуальная машина, NAT, мост, снимок состояния</t>
+          <t xml:space="preserve">непрерывная интеграция, непрерывная доставка, workflow, job, шаг, секрет</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31-32</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -937,20 +937,20 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Профилирование</t>
+          <t xml:space="preserve">Практика 9. VirtualBox; GitHub Actions</t>
         </is>
       </c>
       <c r="D31" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профилируете медленную функцию учебного проекта, находите узкое место по отчёту и сдаёте исправленный вариант с замером времени до и после.</t>
+          <t xml:space="preserve">Поднимаете учебную Linux в VirtualBox с пробросом порта по SSH и настраиваете workflow GitHub Actions, который собирает проект при каждом push.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">профилировщик, узкое место, замер времени, оптимизация, отчёт</t>
+          <t xml:space="preserve">NAT, проброс порта, SSH, workflow, виртуальная машина, гостевая ОС</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. CI/CD и GitHub Actions</t>
+          <t xml:space="preserve">Практика 10. Автоматизация проверок</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -975,12 +975,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете конвейер CI/CD: что запускается на каждый коммит, из каких шагов состоит workflow и где хранятся секреты.</t>
+          <t xml:space="preserve">Собираете локальный скрипт проверок: линтер, тесты и сборка одной командой, и сдаёте конфигурацию, которая возвращает понятный код ошибки.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">непрерывная интеграция, непрерывная доставка, workflow, job, шаг, секрет</t>
+          <t xml:space="preserve">скрипт проверок, линтер, тесты, сборка, код возврата</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. Мини-проект</t>
+          <t xml:space="preserve">Лекция 18. Документирование кода</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1005,16 +1005,16 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Собираете небольшой проект целиком: репозиторий, окружение, сборка, тесты и README, и сдаёте ссылку с проходящим workflow проверок.</t>
+          <t xml:space="preserve">Разбираете, как документировать код изнутри: docstring, комментарии к сложным местам и автогенерация справки из аннотаций.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">мини-проект, репозиторий, workflow, тесты, README</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t xml:space="preserve">docstring, комментарий, аннотация типа, автодокументация, стиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">35</t>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 18. Документирование кода</t>
+          <t xml:space="preserve">Практика 11. Документирование</t>
         </is>
       </c>
       <c r="D34" s="6">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, как документировать код изнутри: docstring, комментарии к сложным местам и автогенерация справки из аннотаций.</t>
+          <t xml:space="preserve">Оформляете документацию к учебному проекту: README с установкой и запуском, описание структуры, и сдаёте документ, по которому проект запускает другой студент.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">docstring, комментарий, аннотация типа, автодокументация, стиль</t>
+          <t xml:space="preserve">README, инструкция запуска, структура проекта, Markdown, документация</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 12. Автоматизация проверок</t>
+          <t xml:space="preserve">Лекция 19. Выбор инструментов под задачу</t>
         </is>
       </c>
       <c r="D35" s="6">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Собираете локальный скрипт проверок: линтер, тесты и сборка одной командой, и сдаёте конфигурацию, которая возвращает понятный код ошибки.</t>
+          <t xml:space="preserve">Разбираете критерии выбора инструмента: размер проекта, язык, требования к сборке и стоимость поддержки, и сравниваете пары альтернатив.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">скрипт проверок, линтер, тесты, сборка, код возврата</t>
+          <t xml:space="preserve">критерии выбора, альтернатива, стоимость поддержки, масштаб проекта, экосистема</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 19. Выбор инструментов под задачу</t>
+          <t xml:space="preserve">Практика 12. Мини-проект</t>
         </is>
       </c>
       <c r="D36" s="6">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете критерии выбора инструмента: размер проекта, язык, требования к сборке и стоимость поддержки, и сравниваете пары альтернатив.</t>
+          <t xml:space="preserve">Собираете небольшой проект целиком: репозиторий, окружение, сборка, тесты и README, и сдаёте ссылку с проходящим workflow проверок.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">критерии выбора, альтернатива, стоимость поддержки, масштаб проекта, экосистема</t>
+          <t xml:space="preserve">мини-проект, репозиторий, workflow, тесты, README</t>
         </is>
       </c>
     </row>

--- a/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
+++ b/courses/2/dev-tools/dist/Учебный_план_Инструментальные_средства_разработки_ПО.xlsx
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оформляете документацию к учебному проекту: README с установкой и запуском, описание структуры, и сдаёте документ, по которому проект запускает другой студент.</t>
+          <t xml:space="preserve">Оформляете документацию к учебному проекту: README с установкой и запуском, описание структуры, и сдаёте документ, по которому проект запускает другой человек.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
